--- a/astro-site/public/dl/plan-negocio-parrillero-asador-eventos/checklist-apertura-parrillero-asador-eventos.xlsx
+++ b/astro-site/public/dl/plan-negocio-parrillero-asador-eventos/checklist-apertura-parrillero-asador-eventos.xlsx
@@ -14,7 +14,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="F5 - Captacion B2C y B2B" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="F6 - Operativa primer evento y postventa" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'F1 - Constitucion y legal'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'F2 - Seguros y cobertura'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'F3 - Equipamiento y proveedores carne'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'F4 - Marca, web y materiales venta'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'F5 - Captacion B2C y B2B'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'F6 - Operativa primer evento y postventa'!$4:$4</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -488,7 +495,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -514,6 +521,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -892,10 +900,19 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -903,7 +920,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -929,6 +946,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1200,10 +1218,19 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1211,7 +1238,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1237,6 +1264,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1724,10 +1752,19 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1735,7 +1772,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1761,6 +1798,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -2178,10 +2216,19 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -2189,7 +2236,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -2215,6 +2262,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -2624,10 +2672,19 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -2635,7 +2692,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -2661,6 +2718,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -3108,9 +3166,18 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>